--- a/data/trans_dic/P34B03_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P34B03_R-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que realiza alguna actividad física moderada, como montar en bicicleta, gimnasia, aeróbic,correr, natación, 3 veces por semana o más</t>
+          <t>Población que realiza alguna actividad física moderada, como montar en bicicleta, gimnasia, aeróbic, correr, natación, durante más de 30 minutos, 3 veces por semana o más (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,89; 24,38</t>
+          <t>15,08; 24,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>21,17; 31,95</t>
+          <t>21,3; 31,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,96; 33,24</t>
+          <t>19,02; 34,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,59; 16,92</t>
+          <t>8,28; 16,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,48; 17,76</t>
+          <t>9,57; 18,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,25; 16,76</t>
+          <t>9,09; 16,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,99; 19,27</t>
+          <t>13,0; 19,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,65; 23,14</t>
+          <t>16,51; 23,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,69; 24,01</t>
+          <t>15,27; 23,62</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,49; 22,92</t>
+          <t>15,67; 23,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,68; 21,74</t>
+          <t>14,94; 21,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,12; 21,24</t>
+          <t>11,92; 22,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,24; 8,69</t>
+          <t>4,12; 8,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,55; 12,49</t>
+          <t>7,3; 12,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,26; 6,77</t>
+          <t>3,18; 7,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,37; 14,83</t>
+          <t>10,38; 14,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,86; 16,2</t>
+          <t>11,88; 16,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,41; 13,71</t>
+          <t>8,05; 13,49</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,34; 18,02</t>
+          <t>9,86; 17,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,26; 23,48</t>
+          <t>14,71; 23,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,51; 24,94</t>
+          <t>15,15; 25,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,9; 8,09</t>
+          <t>2,91; 8,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,19; 14,75</t>
+          <t>8,32; 15,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,48; 9,73</t>
+          <t>4,31; 10,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,0; 11,34</t>
+          <t>6,88; 11,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,6; 17,92</t>
+          <t>12,44; 17,94</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,19; 15,62</t>
+          <t>9,98; 15,46</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,79; 20,07</t>
+          <t>12,07; 20,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,11; 21,39</t>
+          <t>13,27; 21,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,13; 24,38</t>
+          <t>12,89; 23,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,78; 8,68</t>
+          <t>3,91; 9,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,38; 11,12</t>
+          <t>5,18; 11,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,71; 14,17</t>
+          <t>5,92; 14,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,64; 13,27</t>
+          <t>8,76; 13,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,84; 15,18</t>
+          <t>10,03; 15,0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,4; 16,74</t>
+          <t>9,24; 16,42</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,35; 17,86</t>
+          <t>8,45; 17,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,78; 13,56</t>
+          <t>5,88; 13,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,65; 23,0</t>
+          <t>12,35; 23,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,45; 11,34</t>
+          <t>4,52; 11,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,95; 9,22</t>
+          <t>2,91; 8,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,12; 9,41</t>
+          <t>4,21; 9,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,25; 13,14</t>
+          <t>7,41; 13,05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,94; 10,11</t>
+          <t>4,96; 10,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,72; 14,24</t>
+          <t>8,71; 14,46</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10,66; 19,12</t>
+          <t>10,69; 18,87</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16,26; 27,07</t>
+          <t>16,21; 26,32</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,55; 14,18</t>
+          <t>6,64; 14,86</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,85; 7,24</t>
+          <t>1,87; 7,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,96; 15,25</t>
+          <t>7,58; 15,12</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,08; 8,26</t>
+          <t>2,92; 7,84</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,69; 11,64</t>
+          <t>6,89; 12,02</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13,03; 19,33</t>
+          <t>13,05; 19,48</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,47; 10,0</t>
+          <t>5,47; 10,18</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>12,42; 18,91</t>
+          <t>12,28; 18,74</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,87; 18,68</t>
+          <t>12,66; 18,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,54; 20,91</t>
+          <t>13,84; 21,1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,81; 9,86</t>
+          <t>5,63; 9,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,16; 14,03</t>
+          <t>9,55; 14,4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,82; 11,35</t>
+          <t>3,54; 11,31</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,6; 13,45</t>
+          <t>9,66; 13,31</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11,81; 15,53</t>
+          <t>11,56; 15,39</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,96; 14,51</t>
+          <t>7,67; 14,63</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>11,83; 16,99</t>
+          <t>11,59; 16,62</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10,59; 15,48</t>
+          <t>10,95; 15,62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,19; 19,61</t>
+          <t>6,61; 19,71</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,06; 7,22</t>
+          <t>4,08; 7,3</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,94; 8,58</t>
+          <t>4,92; 8,48</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,25; 11,0</t>
+          <t>7,31; 11,11</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,31; 11,32</t>
+          <t>8,21; 11,3</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,36; 11,48</t>
+          <t>8,35; 11,34</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,94; 14,41</t>
+          <t>7,24; 14,37</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>14,35; 16,95</t>
+          <t>14,27; 16,76</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>15,63; 18,2</t>
+          <t>15,51; 18,11</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13,25; 18,7</t>
+          <t>12,87; 18,64</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,74; 7,56</t>
+          <t>5,77; 7,47</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8,45; 10,5</t>
+          <t>8,51; 10,54</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,33; 9,03</t>
+          <t>6,4; 8,97</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,26; 11,78</t>
+          <t>10,21; 11,8</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>12,31; 13,96</t>
+          <t>12,27; 13,89</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>10,5; 13,27</t>
+          <t>10,5; 13,31</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que realiza alguna actividad física moderada, como montar en bicicleta, gimnasia, aeróbic,correr, natación, 3 veces por semana o más</t>
+          <t>Población que realiza alguna actividad física moderada, como montar en bicicleta, gimnasia, aeróbic, correr, natación, durante más de 30 minutos, 3 veces por semana o más (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>43700; 71582</t>
+          <t>44263; 72872</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>62183; 93854</t>
+          <t>62571; 93875</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>59059; 103521</t>
+          <t>59236; 107187</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24672; 48588</t>
+          <t>23791; 48124</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>27359; 51277</t>
+          <t>27633; 52844</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26801; 48556</t>
+          <t>26336; 48971</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>75441; 111902</t>
+          <t>75532; 111986</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>97007; 134762</t>
+          <t>96176; 135422</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>94314; 144315</t>
+          <t>91789; 141969</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>78299; 115882</t>
+          <t>79238; 117489</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>73771; 109283</t>
+          <t>75065; 108779</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>62831; 110085</t>
+          <t>61780; 114211</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22119; 45368</t>
+          <t>21475; 43704</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>39492; 65315</t>
+          <t>38175; 65490</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16814; 34862</t>
+          <t>16386; 36050</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>106583; 152320</t>
+          <t>106646; 151427</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>121593; 166120</t>
+          <t>121798; 168401</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>86932; 141638</t>
+          <t>83139; 139381</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>33504; 58381</t>
+          <t>31951; 55891</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>48601; 74809</t>
+          <t>46854; 75837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>45861; 78818</t>
+          <t>47892; 79808</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9900; 27581</t>
+          <t>9919; 27547</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>27544; 49612</t>
+          <t>27990; 51426</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15627; 33980</t>
+          <t>15064; 35215</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>46561; 75428</t>
+          <t>45740; 75274</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>82508; 117380</t>
+          <t>81483; 117454</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>67807; 103934</t>
+          <t>66363; 102841</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>44080; 75073</t>
+          <t>45129; 75155</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>48516; 79132</t>
+          <t>49104; 79675</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>41033; 76193</t>
+          <t>40292; 73893</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14705; 33750</t>
+          <t>15192; 35217</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>20825; 43064</t>
+          <t>20063; 43039</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>27169; 67431</t>
+          <t>28151; 68362</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>65935; 101275</t>
+          <t>66847; 102030</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>74499; 114938</t>
+          <t>75951; 113616</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>74108; 131932</t>
+          <t>72843; 129455</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>17763; 37970</t>
+          <t>17965; 37911</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>12218; 28646</t>
+          <t>12416; 29430</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22615; 41107</t>
+          <t>22071; 41221</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9762; 24910</t>
+          <t>9924; 25583</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6452; 20151</t>
+          <t>6370; 19252</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8582; 19602</t>
+          <t>8764; 19408</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31316; 56800</t>
+          <t>32019; 56423</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>21239; 43440</t>
+          <t>21335; 43242</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>33749; 55096</t>
+          <t>33702; 55982</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>29214; 52383</t>
+          <t>29287; 51704</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>42796; 71238</t>
+          <t>42645; 69263</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17667; 38225</t>
+          <t>17898; 40057</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5167; 20280</t>
+          <t>5230; 19756</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>21732; 41637</t>
+          <t>20692; 41294</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7924; 21227</t>
+          <t>7502; 20157</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>37041; 64511</t>
+          <t>38156; 66568</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>69875; 103631</t>
+          <t>69971; 104448</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>28797; 52673</t>
+          <t>28828; 53612</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>82201; 125148</t>
+          <t>81268; 124057</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>84526; 122661</t>
+          <t>83125; 122211</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>84253; 130122</t>
+          <t>86151; 131335</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>40321; 68418</t>
+          <t>39031; 68537</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>63327; 96966</t>
+          <t>66046; 99566</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>32367; 96293</t>
+          <t>30055; 95915</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>130109; 182298</t>
+          <t>130966; 180402</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>159125; 209313</t>
+          <t>155772; 207446</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>102373; 213356</t>
+          <t>112795; 215042</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>92171; 132337</t>
+          <t>90288; 129461</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>82438; 120501</t>
+          <t>85244; 121587</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>57514; 182092</t>
+          <t>61351; 183014</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>33418; 59506</t>
+          <t>33595; 60123</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>40789; 70918</t>
+          <t>40657; 70075</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>51774; 78515</t>
+          <t>52154; 79277</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>133134; 181523</t>
+          <t>131640; 181081</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>134158; 184222</t>
+          <t>133918; 181949</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>113949; 236698</t>
+          <t>118851; 236092</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>491617; 580500</t>
+          <t>488666; 574007</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>530515; 617833</t>
+          <t>526414; 614737</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>458096; 646747</t>
+          <t>445002; 644667</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>204231; 268913</t>
+          <t>205139; 265688</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>299589; 372128</t>
+          <t>301638; 373426</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>231399; 330164</t>
+          <t>234173; 327856</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>716225; 822701</t>
+          <t>712616; 823438</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>854371; 968685</t>
+          <t>851221; 963781</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>747120; 943736</t>
+          <t>746871; 946601</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P34B03_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P34B03_R-Provincia-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>16,26%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,08; 24,82</t>
+          <t>14,8; 24,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>21,3; 31,96</t>
+          <t>21,15; 32,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19,02; 34,42</t>
+          <t>16,82; 27,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,28; 16,75</t>
+          <t>8,1; 16,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,57; 18,3</t>
+          <t>9,27; 18,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,09; 16,91</t>
+          <t>8,43; 14,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,0; 19,28</t>
+          <t>12,97; 19,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,51; 23,25</t>
+          <t>16,56; 23,38</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,27; 23,62</t>
+          <t>13,35; 19,66</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,24%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,67; 23,24</t>
+          <t>15,35; 23,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,94; 21,64</t>
+          <t>14,83; 21,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,92; 22,03</t>
+          <t>11,93; 20,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,12; 8,37</t>
+          <t>4,06; 8,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,3; 12,52</t>
+          <t>7,61; 12,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,18; 7,0</t>
+          <t>3,17; 6,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,38; 14,74</t>
+          <t>10,32; 14,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,88; 16,42</t>
+          <t>12,04; 16,32</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,05; 13,49</t>
+          <t>8,17; 12,74</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,68%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,86; 17,25</t>
+          <t>10,52; 17,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,71; 23,81</t>
+          <t>15,2; 24,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,15; 25,25</t>
+          <t>15,07; 24,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,91; 8,08</t>
+          <t>2,94; 7,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,32; 15,29</t>
+          <t>8,19; 14,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,31; 10,09</t>
+          <t>4,33; 9,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,88; 11,32</t>
+          <t>6,8; 11,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,44; 17,94</t>
+          <t>12,41; 18,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,98; 15,46</t>
+          <t>10,06; 15,59</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>14,76%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,07; 20,1</t>
+          <t>11,78; 19,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,27; 21,54</t>
+          <t>12,97; 21,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,89; 23,64</t>
+          <t>12,45; 22,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,91; 9,05</t>
+          <t>3,87; 8,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,18; 11,11</t>
+          <t>5,44; 10,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,92; 14,37</t>
+          <t>9,67; 16,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,76; 13,37</t>
+          <t>8,49; 13,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,03; 15,0</t>
+          <t>10,11; 15,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,24; 16,42</t>
+          <t>11,97; 18,22</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>12,33%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,45; 17,83</t>
+          <t>8,27; 17,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,88; 13,93</t>
+          <t>5,71; 14,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,35; 23,06</t>
+          <t>14,01; 24,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,52; 11,65</t>
+          <t>4,6; 11,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,91; 8,81</t>
+          <t>2,96; 9,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,21; 9,32</t>
+          <t>4,45; 10,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,41; 13,05</t>
+          <t>7,36; 13,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,96; 10,06</t>
+          <t>5,09; 10,1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,71; 14,46</t>
+          <t>9,61; 15,67</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10,69; 18,87</t>
+          <t>10,26; 18,88</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16,21; 26,32</t>
+          <t>16,51; 27,03</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,64; 14,86</t>
+          <t>6,39; 13,49</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,87; 7,05</t>
+          <t>2,07; 7,13</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,58; 15,12</t>
+          <t>7,77; 15,26</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,92; 7,84</t>
+          <t>2,77; 8,17</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,89; 12,02</t>
+          <t>6,96; 12,09</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13,05; 19,48</t>
+          <t>12,96; 19,46</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,47; 10,18</t>
+          <t>5,44; 9,89</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>13,58%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>12,28; 18,74</t>
+          <t>12,51; 18,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,66; 18,61</t>
+          <t>12,79; 18,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,84; 21,1</t>
+          <t>13,58; 20,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,63; 9,88</t>
+          <t>5,72; 10,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,55; 14,4</t>
+          <t>9,37; 14,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,54; 11,31</t>
+          <t>8,63; 12,79</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,66; 13,31</t>
+          <t>9,63; 13,36</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11,56; 15,39</t>
+          <t>11,77; 15,59</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,67; 14,63</t>
+          <t>11,58; 15,68</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>14,13%</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>11,59; 16,62</t>
+          <t>11,68; 16,69</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10,95; 15,62</t>
+          <t>11,01; 15,69</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,61; 19,71</t>
+          <t>16,39; 22,8</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,08; 7,3</t>
+          <t>4,11; 7,39</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,92; 8,48</t>
+          <t>5,11; 8,6</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,31; 11,11</t>
+          <t>7,45; 11,39</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,21; 11,3</t>
+          <t>8,27; 11,18</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,35; 11,34</t>
+          <t>8,39; 11,31</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7,24; 14,37</t>
+          <t>12,26; 16,19</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,95%</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>14,27; 16,76</t>
+          <t>14,36; 16,96</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>15,51; 18,11</t>
+          <t>15,55; 18,06</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12,87; 18,64</t>
+          <t>15,85; 19,02</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,77; 7,47</t>
+          <t>5,74; 7,54</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8,51; 10,54</t>
+          <t>8,56; 10,49</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,4; 8,97</t>
+          <t>7,82; 9,6</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,21; 11,8</t>
+          <t>10,22; 11,72</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>12,27; 13,89</t>
+          <t>12,21; 13,94</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>10,5; 13,31</t>
+          <t>12,06; 13,81</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>78792</t>
+          <t>68504</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36563</t>
+          <t>34706</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>115355</t>
+          <t>103210</t>
         </is>
       </c>
     </row>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>44263; 72872</t>
+          <t>43442; 70813</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>62571; 93875</t>
+          <t>62130; 94517</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>59236; 107187</t>
+          <t>53624; 87873</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23791; 48124</t>
+          <t>23281; 48549</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>27633; 52844</t>
+          <t>26768; 52093</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26336; 48971</t>
+          <t>26659; 46842</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>75532; 111986</t>
+          <t>75340; 111918</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>96176; 135422</t>
+          <t>96456; 136203</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>91789; 141969</t>
+          <t>84769; 124805</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>85353</t>
+          <t>84857</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>24436</t>
+          <t>25478</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>109790</t>
+          <t>110335</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>79238; 117489</t>
+          <t>77576; 116394</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>75065; 108779</t>
+          <t>74522; 108348</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>61780; 114211</t>
+          <t>63308; 110262</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21475; 43704</t>
+          <t>21201; 44633</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>38175; 65490</t>
+          <t>39804; 67915</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16386; 36050</t>
+          <t>17331; 37030</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>106646; 151427</t>
+          <t>106022; 151068</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>121798; 168401</t>
+          <t>123495; 167425</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>83139; 139381</t>
+          <t>88047; 137209</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60501</t>
+          <t>61530</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23305</t>
+          <t>23699</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>83806</t>
+          <t>85229</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>31951; 55891</t>
+          <t>34098; 56891</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>46854; 75837</t>
+          <t>48424; 76517</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>47892; 79808</t>
+          <t>47632; 78555</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9919; 27547</t>
+          <t>10025; 27012</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>27990; 51426</t>
+          <t>27539; 49483</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15064; 35215</t>
+          <t>15439; 34572</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>45740; 75274</t>
+          <t>45210; 75226</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>81483; 117454</t>
+          <t>81243; 118155</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>66363; 102841</t>
+          <t>67631; 104791</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>55304</t>
+          <t>63078</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47143</t>
+          <t>54291</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>102448</t>
+          <t>117368</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>45129; 75155</t>
+          <t>44058; 74747</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>49104; 79675</t>
+          <t>48003; 78983</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>40292; 73893</t>
+          <t>46439; 83481</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15192; 35217</t>
+          <t>15059; 32758</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>20063; 43039</t>
+          <t>21062; 42378</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28151; 68362</t>
+          <t>40821; 71434</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>66847; 102030</t>
+          <t>64778; 100741</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>75951; 113616</t>
+          <t>76562; 114314</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>72843; 129455</t>
+          <t>95135; 144897</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30521</t>
+          <t>38474</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13225</t>
+          <t>14873</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>43746</t>
+          <t>53347</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>17965; 37911</t>
+          <t>17590; 38131</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>12416; 29430</t>
+          <t>12055; 29851</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22071; 41221</t>
+          <t>28805; 50805</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9924; 25583</t>
+          <t>10094; 25888</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6370; 19252</t>
+          <t>6471; 19730</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8764; 19408</t>
+          <t>10090; 22709</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32019; 56423</t>
+          <t>31820; 57104</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>21335; 43242</t>
+          <t>21870; 43412</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>33702; 55982</t>
+          <t>41582; 67792</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>27082</t>
+          <t>26096</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12867</t>
+          <t>12957</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>39949</t>
+          <t>39053</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>29287; 51704</t>
+          <t>28118; 51723</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>42645; 69263</t>
+          <t>43448; 71116</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17898; 40057</t>
+          <t>17290; 36528</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5230; 19756</t>
+          <t>5784; 19968</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>20692; 41294</t>
+          <t>21227; 41676</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7502; 20157</t>
+          <t>7307; 21551</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>38156; 66568</t>
+          <t>38550; 66967</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>69971; 104448</t>
+          <t>69475; 104333</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>28828; 53612</t>
+          <t>29077; 52851</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>105767</t>
+          <t>121616</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>67137</t>
+          <t>80373</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>172904</t>
+          <t>201988</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>81268; 124057</t>
+          <t>82793; 121289</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>83125; 122211</t>
+          <t>83954; 122801</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>86151; 131335</t>
+          <t>97316; 147454</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>39031; 68537</t>
+          <t>39675; 70951</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>66046; 99566</t>
+          <t>64765; 101310</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>30055; 95915</t>
+          <t>66487; 98552</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>130966; 180402</t>
+          <t>130524; 181166</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>155772; 207446</t>
+          <t>158696; 210081</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>112795; 215042</t>
+          <t>172267; 233154</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>127981</t>
+          <t>153770</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>64506</t>
+          <t>76005</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>192488</t>
+          <t>229775</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>90288; 129461</t>
+          <t>91000; 130027</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>85244; 121587</t>
+          <t>85684; 122185</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>61351; 183014</t>
+          <t>130816; 181928</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>33595; 60123</t>
+          <t>33900; 60862</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>40657; 70075</t>
+          <t>42194; 71055</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>52154; 79277</t>
+          <t>61743; 94404</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>131640; 181081</t>
+          <t>132608; 179235</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>133918; 181949</t>
+          <t>134581; 181562</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>118851; 236092</t>
+          <t>199501; 263376</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>571302</t>
+          <t>617923</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>289183</t>
+          <t>322382</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>860485</t>
+          <t>940305</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>488666; 574007</t>
+          <t>491824; 580729</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>526414; 614737</t>
+          <t>527845; 612864</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>445002; 644667</t>
+          <t>559498; 671450</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>205139; 265688</t>
+          <t>204238; 268317</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>301638; 373426</t>
+          <t>303350; 371998</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>234173; 327856</t>
+          <t>291739; 358017</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>712616; 823438</t>
+          <t>713439; 818433</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>851221; 963781</t>
+          <t>847413; 967557</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>746871; 946601</t>
+          <t>875777; 1002298</t>
         </is>
       </c>
     </row>
